--- a/data/contacts.xlsx
+++ b/data/contacts.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,10 +499,8 @@
           <t>ajith@gmail.com</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>9876543210</t>
-        </is>
+      <c r="C3" t="n">
+        <v>9876543210</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -518,6 +516,43 @@
       <c r="G3" t="inlineStr">
         <is>
           <t>2026-04-25 02:57:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ajith t</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ajiththiruppathi00@gmail.com</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>7867840111</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>covai</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>aaa@comp</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>gggrrrttt</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-04-27 02:37:18</t>
         </is>
       </c>
     </row>
